--- a/nnnnn.xlsx
+++ b/nnnnn.xlsx
@@ -55,13 +55,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -433,6 +436,11 @@
   </sheetPr>
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
@@ -457,7 +465,7 @@
           <t>09:00~09:30</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>報到</t>
         </is>
@@ -488,7 +496,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>從 MWC 2026 到 6G：AI-RAN 標準、開源與互通測試的最新進展</t>
+          <t>邁向6G 的AI-RAN及O-RAN 趨勢介紹</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -505,7 +513,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>基於 O-RAN 開放介面的 ISAC 無線感知技術</t>
+          <t>下世代B5G/6G專網應用與未來趨勢</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -520,7 +528,7 @@
           <t>10:30~10:50</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Break</t>
         </is>
@@ -534,8 +542,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Federated Foundational Models in AI-RAN：Practical and
-Forward Looking Perspective</t>
+          <t>從O-RAN到AI-RAN 智慧通訊的節能應用</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -550,6 +557,16 @@
           <t>11:20~12:00</t>
         </is>
       </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>O-RAN環境和各模組化功能介紹</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>教學團隊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -557,7 +574,7 @@
           <t>12:00~13:30</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Lunch</t>
         </is>
@@ -571,7 +588,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>O-RAN 開源軟體組織簡介</t>
+          <t>O-RAN 的市場應用案例</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -586,6 +603,16 @@
           <t>14:00~14:30</t>
         </is>
       </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>O-RAN OSC環境建置教學</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>教學團隊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -593,7 +620,7 @@
           <t>14:30~14:50</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Break</t>
         </is>
@@ -607,7 +634,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>O-RAN xApps 實作建置教學</t>
+          <t>O-RAN OSC第三方應用程式 xApps建置教學</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -622,18 +649,22 @@
           <t>15:50~16:30</t>
         </is>
       </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>現場討論時間</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>教學團隊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="4">
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="C13:C14"/>
     <mergeCell ref="B12:C12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
